--- a/public/informes-templates/SERVICIO DE SOPORTE.xlsx
+++ b/public/informes-templates/SERVICIO DE SOPORTE.xlsx
@@ -1,49 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SIP-APP\SIPAPP-HUAQUIAN\Frontend\public\informes-templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A08A235-113C-4E91-841E-F5C9DB3A0474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679DBAFD-CAFA-4827-BDD0-ED1CDBD455EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="q+/9yjuff96Xo0+NGKOZ+K0awv71L30I1S/Ihp9dmd8="/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -133,9 +101,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -234,7 +203,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -320,15 +289,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -375,21 +335,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -399,10 +347,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -412,19 +358,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -432,15 +366,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -451,44 +376,68 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,68 +456,53 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -773,24 +707,24 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y204"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="8" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="8" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -809,15 +743,15 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
     </row>
-    <row r="2" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
+    <row r="2" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="9"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -836,19 +770,17 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
     </row>
-    <row r="3" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B3" s="27"/>
+    <row r="3" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11"/>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -867,17 +799,17 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
+    <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="6"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -896,17 +828,17 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
     </row>
-    <row r="5" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
+    <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="6"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -925,17 +857,17 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29"/>
+    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="6"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -954,17 +886,17 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
     </row>
-    <row r="7" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
+    <row r="7" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="6"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -983,17 +915,17 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
     </row>
-    <row r="8" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
+    <row r="8" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="6"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1012,17 +944,17 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
     </row>
-    <row r="9" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
+    <row r="9" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="6"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1041,17 +973,17 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
+    <row r="10" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
       <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="6"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1070,17 +1002,17 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
+    <row r="11" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="16"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1099,17 +1031,17 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
+    <row r="12" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="6"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="16"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1138,7 +1070,7 @@
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="H13" s="18"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1158,16 +1090,16 @@
       <c r="Y13" s="1"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1187,16 +1119,16 @@
       <c r="Y14" s="1"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="6"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1216,16 +1148,16 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1245,16 +1177,16 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1274,16 +1206,16 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1303,16 +1235,16 @@
       <c r="Y18" s="1"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1332,16 +1264,16 @@
       <c r="Y19" s="1"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1361,16 +1293,16 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="6"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="16"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1389,17 +1321,17 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
     </row>
-    <row r="22" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="6"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1418,15 +1350,15 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
     </row>
-    <row r="23" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="10"/>
+    <row r="23" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
       <c r="E23" s="25"/>
-      <c r="F23" s="10"/>
+      <c r="F23" s="26"/>
       <c r="G23" s="25"/>
-      <c r="H23" s="10"/>
+      <c r="H23" s="26"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1445,15 +1377,15 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
-    <row r="24" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="22"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="23"/>
+    <row r="24" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="28"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1472,15 +1404,15 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
-    <row r="25" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="23"/>
+    <row r="25" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="28"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1499,15 +1431,15 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="23"/>
+    <row r="26" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="28"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1526,15 +1458,15 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="23"/>
+    <row r="27" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -1553,15 +1485,15 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="23"/>
+    <row r="28" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="28"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1580,15 +1512,15 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="23"/>
+    <row r="29" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="27"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="28"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -1607,15 +1539,15 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="22"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="23"/>
+    <row r="30" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="27"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="28"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1634,15 +1566,15 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="23"/>
+    <row r="31" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="27"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="28"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1661,15 +1593,15 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
     </row>
-    <row r="32" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="23"/>
+    <row r="32" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="27"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="28"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1688,15 +1620,15 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
     </row>
-    <row r="33" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="22"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="23"/>
+    <row r="33" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="27"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="28"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1715,15 +1647,15 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
     </row>
-    <row r="34" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="22"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23"/>
+    <row r="34" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="27"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="28"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -1742,15 +1674,15 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
     </row>
-    <row r="35" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="23"/>
+    <row r="35" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="28"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -1769,15 +1701,15 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A36" s="22"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="23"/>
+    <row r="36" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="27"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="28"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -1796,15 +1728,15 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A37" s="14"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="16"/>
+    <row r="37" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="30"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -1823,19 +1755,19 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="26" t="s">
+    <row r="38" spans="1:25" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="26" t="s">
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="10"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="6"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -1854,17 +1786,17 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="6"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="16"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -1883,15 +1815,15 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
     </row>
-    <row r="40" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="6"/>
+    <row r="40" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="16"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -1910,15 +1842,15 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
     </row>
-    <row r="41" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="6"/>
+    <row r="41" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="16"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -1937,15 +1869,15 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
     </row>
-    <row r="42" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="6"/>
+    <row r="42" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="16"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -1964,15 +1896,15 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
     </row>
-    <row r="43" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="6"/>
+    <row r="43" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="16"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -1991,17 +1923,17 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A44" s="7" t="s">
+    <row r="44" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="6"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="16"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2020,15 +1952,15 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
     </row>
-    <row r="45" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A45" s="4"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="6"/>
+    <row r="45" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="16"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -2047,15 +1979,15 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
     </row>
-    <row r="46" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="6"/>
+    <row r="46" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="16"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -2074,15 +2006,15 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
     </row>
-    <row r="47" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="6"/>
+    <row r="47" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="16"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2101,15 +2033,15 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
     </row>
-    <row r="48" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="6"/>
+    <row r="48" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="16"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2128,17 +2060,17 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A49" s="7" t="s">
+    <row r="49" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="6"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="16"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2157,15 +2089,15 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
     </row>
-    <row r="50" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="6"/>
+    <row r="50" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="24"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="16"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2184,15 +2116,15 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
     </row>
-    <row r="51" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="6"/>
+    <row r="51" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="24"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="16"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2211,15 +2143,15 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
     </row>
-    <row r="52" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="6"/>
+    <row r="52" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="24"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="16"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2238,15 +2170,15 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
     </row>
-    <row r="53" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="6"/>
+    <row r="53" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="24"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="16"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2265,7 +2197,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
     </row>
-    <row r="54" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2292,7 +2224,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2319,7 +2251,7 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
     </row>
-    <row r="56" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2346,7 +2278,7 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
     </row>
-    <row r="57" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2373,7 +2305,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
     </row>
-    <row r="58" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2400,7 +2332,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
     </row>
-    <row r="59" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2427,7 +2359,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
     </row>
-    <row r="60" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2454,7 +2386,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2481,7 +2413,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
     </row>
-    <row r="62" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2508,7 +2440,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
     </row>
-    <row r="63" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2535,7 +2467,7 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
     </row>
-    <row r="64" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2562,7 +2494,7 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
     </row>
-    <row r="65" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2589,7 +2521,7 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
     </row>
-    <row r="66" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2616,7 +2548,7 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
     </row>
-    <row r="67" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2643,7 +2575,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
     </row>
-    <row r="68" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2670,7 +2602,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row r="69" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2697,7 +2629,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row r="70" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2724,7 +2656,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
     </row>
-    <row r="71" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2751,7 +2683,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row r="72" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2778,7 +2710,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2805,7 +2737,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2832,7 +2764,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row r="75" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2859,7 +2791,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
     </row>
-    <row r="76" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2886,7 +2818,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
     </row>
-    <row r="77" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2913,7 +2845,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
     </row>
-    <row r="78" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2940,7 +2872,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2967,7 +2899,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
     </row>
-    <row r="80" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2994,7 +2926,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3021,7 +2953,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3048,7 +2980,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3075,7 +3007,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row r="84" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3102,7 +3034,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row r="85" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3129,7 +3061,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3156,7 +3088,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3183,7 +3115,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row r="88" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3210,7 +3142,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
     </row>
-    <row r="89" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3237,7 +3169,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3264,7 +3196,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
     </row>
-    <row r="91" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3291,7 +3223,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3318,7 +3250,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3345,7 +3277,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3372,7 +3304,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3399,7 +3331,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3426,7 +3358,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3453,7 +3385,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3480,7 +3412,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row r="99" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3507,7 +3439,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3534,7 +3466,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3561,7 +3493,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3588,7 +3520,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3615,7 +3547,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3642,7 +3574,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3669,7 +3601,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3696,7 +3628,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
     </row>
-    <row r="107" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3723,7 +3655,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
     </row>
-    <row r="108" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3750,7 +3682,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
     </row>
-    <row r="109" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3777,7 +3709,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
     </row>
-    <row r="110" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3804,7 +3736,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
     </row>
-    <row r="111" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3831,7 +3763,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3858,7 +3790,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
     </row>
-    <row r="113" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3885,7 +3817,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
     </row>
-    <row r="114" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3912,7 +3844,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
     </row>
-    <row r="115" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3939,7 +3871,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
     </row>
-    <row r="116" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3966,7 +3898,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
     </row>
-    <row r="117" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3993,7 +3925,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
     </row>
-    <row r="118" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4020,7 +3952,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
     </row>
-    <row r="119" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4047,7 +3979,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
     </row>
-    <row r="120" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4074,7 +4006,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
     </row>
-    <row r="121" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4101,7 +4033,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
     </row>
-    <row r="122" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4128,7 +4060,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
     </row>
-    <row r="123" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4155,7 +4087,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
     </row>
-    <row r="124" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4182,7 +4114,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
     </row>
-    <row r="125" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4209,7 +4141,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
     </row>
-    <row r="126" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4236,7 +4168,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
     </row>
-    <row r="127" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4263,7 +4195,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
     </row>
-    <row r="128" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4290,7 +4222,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
     </row>
-    <row r="129" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4317,7 +4249,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4344,7 +4276,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
     </row>
-    <row r="131" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4371,7 +4303,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
     </row>
-    <row r="132" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4398,7 +4330,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
     </row>
-    <row r="133" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4425,7 +4357,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
     </row>
-    <row r="134" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4452,7 +4384,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
     </row>
-    <row r="135" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4479,7 +4411,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
     </row>
-    <row r="136" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4506,7 +4438,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
     </row>
-    <row r="137" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4533,7 +4465,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
     </row>
-    <row r="138" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4560,7 +4492,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
     </row>
-    <row r="139" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4587,7 +4519,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
     </row>
-    <row r="140" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4614,7 +4546,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
     </row>
-    <row r="141" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4641,7 +4573,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
     </row>
-    <row r="142" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4668,7 +4600,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
     </row>
-    <row r="143" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4695,7 +4627,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
     </row>
-    <row r="144" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4722,7 +4654,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
     </row>
-    <row r="145" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4749,7 +4681,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
     </row>
-    <row r="146" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4776,7 +4708,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
     </row>
-    <row r="147" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4803,7 +4735,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
     </row>
-    <row r="148" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4830,7 +4762,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
     </row>
-    <row r="149" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4857,7 +4789,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
     </row>
-    <row r="150" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4884,7 +4816,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
     </row>
-    <row r="151" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4911,7 +4843,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
     </row>
-    <row r="152" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4938,7 +4870,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
     </row>
-    <row r="153" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4965,7 +4897,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
     </row>
-    <row r="154" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4992,7 +4924,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
     </row>
-    <row r="155" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5019,7 +4951,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
     </row>
-    <row r="156" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5046,7 +4978,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
     </row>
-    <row r="157" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5073,7 +5005,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
     </row>
-    <row r="158" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5100,7 +5032,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
     </row>
-    <row r="159" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5127,7 +5059,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
     </row>
-    <row r="160" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5154,7 +5086,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
     </row>
-    <row r="161" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5181,7 +5113,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
     </row>
-    <row r="162" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5208,7 +5140,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
     </row>
-    <row r="163" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5235,7 +5167,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
     </row>
-    <row r="164" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5262,7 +5194,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
     </row>
-    <row r="165" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5289,7 +5221,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
     </row>
-    <row r="166" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5316,7 +5248,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
     </row>
-    <row r="167" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5343,7 +5275,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
     </row>
-    <row r="168" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5370,7 +5302,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
     </row>
-    <row r="169" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5397,7 +5329,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
     </row>
-    <row r="170" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5424,7 +5356,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
     </row>
-    <row r="171" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5451,7 +5383,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
     </row>
-    <row r="172" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5478,7 +5410,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
     </row>
-    <row r="173" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5505,7 +5437,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
     </row>
-    <row r="174" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5532,7 +5464,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
     </row>
-    <row r="175" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5559,7 +5491,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
     </row>
-    <row r="176" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5586,7 +5518,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
     </row>
-    <row r="177" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5613,7 +5545,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
     </row>
-    <row r="178" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5640,7 +5572,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
     </row>
-    <row r="179" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5667,7 +5599,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
     </row>
-    <row r="180" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5694,7 +5626,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
     </row>
-    <row r="181" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5721,7 +5653,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
     </row>
-    <row r="182" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5748,7 +5680,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
     </row>
-    <row r="183" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5775,7 +5707,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
     </row>
-    <row r="184" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5802,7 +5734,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
     </row>
-    <row r="185" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5829,7 +5761,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
     </row>
-    <row r="186" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5856,7 +5788,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
     </row>
-    <row r="187" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5883,7 +5815,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
     </row>
-    <row r="188" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5910,7 +5842,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
     </row>
-    <row r="189" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5937,7 +5869,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
     </row>
-    <row r="190" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5964,7 +5896,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
     </row>
-    <row r="191" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5991,7 +5923,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
     </row>
-    <row r="192" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6018,7 +5950,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6045,7 +5977,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
     </row>
-    <row r="194" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6072,7 +6004,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
     </row>
-    <row r="195" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6099,7 +6031,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6126,7 +6058,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
     </row>
-    <row r="197" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6153,7 +6085,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
     </row>
-    <row r="198" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6180,7 +6112,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
     </row>
-    <row r="199" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6207,7 +6139,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
     </row>
-    <row r="200" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6234,7 +6166,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
     </row>
-    <row r="201" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6261,7 +6193,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
     </row>
-    <row r="202" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6288,7 +6220,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
     </row>
-    <row r="203" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6315,7 +6247,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
     </row>
-    <row r="204" spans="1:25" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6343,61 +6275,58 @@
       <c r="Y204" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A3:B12"/>
-    <mergeCell ref="A23:B37"/>
-    <mergeCell ref="C23:D37"/>
-    <mergeCell ref="E23:F37"/>
-    <mergeCell ref="G23:H37"/>
+  <mergeCells count="47">
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="E38:H38"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:H19"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="C20:H20"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:H21"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:H15"/>
     <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:B12"/>
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="D5:H5"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="D7:H7"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="C18:H18"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="D12:H12"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A51:H51"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
+  <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>